--- a/genon/preprocessor/manual/custom_fields_runtime_exceptions.xlsx
+++ b/genon/preprocessor/manual/custom_fields_runtime_exceptions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shkim/_shkim/01.source/doc_parser/genon/preprocessor/facade/gitbook_doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shkim/_shkim/01.dev/doc_parser/genon/preprocessor/manual/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157ECF1F-5169-1348-B6C3-086E4DB08BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB6428A-918F-1842-99A8-AB2AA304C951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="parser,chunker" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'parser,chunker'!$B$1:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'parser,chunker'!$B$1:$D$23</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="55">
   <si>
     <t>단계</t>
   </si>
@@ -75,6 +75,15 @@
   - 엑셀 제목 행에 같은 열 이름이 둘 이상 있음</t>
   </si>
   <si>
+    <t>"레코드 배열 후보 […] 를 fields 의 alias 로 구별할 수 없습니다. source.records_at 에 배열 키를 지정하세요."</t>
+  </si>
+  <si>
+    <t>• 문서 구조가 모호해 어느 값을 써야 할지 정할 수 없음
+  - 설정에 레코드 위치(records_at)를 적지 않으면 JSON 안의 목록을 자동으로 찾음 → 후보 목록이 여럿인데 설정의 항목 이름만으로는 어느 것인지 가릴 수 없음
+  - 어느 후보에서도 설정의 항목 이름에 해당하는 값을 찾지 못한 경우도 포함
+  - missing_policy 설정과 무관하게 실패 → 설정에 records_at 을 지정하면 해소</t>
+  </si>
+  <si>
     <t>"Markdown front matter 중복 키: …"</t>
   </si>
   <si>
@@ -140,6 +149,17 @@
   - LLM 앞단 게이트웨이가 오류를 정상 응답(200)에 담아 보내는 경우가 대표적</t>
   </si>
   <si>
+    <t>TypeError</t>
+  </si>
+  <si>
+    <t>"extractor: python 의 결과는 dict 이어야 합니다: &lt;타입&gt;" / "custom_fields parser 결과는 dict 이어야 합니다."</t>
+  </si>
+  <si>
+    <t>• 직접 작성한 처리 함수의 반환값이 약속된 형식이 아님
+  - python 추출 함수나 LLM 응답 해석 함수(parser)가 dict 가 아닌 값을 돌려줌
+  - 기본 설정(error_policy: lenient)은 경고만 남기고 진행 → error_policy: strict 로 바꾼 경우에만 실패</t>
+  </si>
+  <si>
     <t>chunker</t>
   </si>
   <si>
@@ -187,19 +207,3094 @@
   - 설정의 필수값 조건을 채우지 못해 파서 단계에서 모든 항목이 제외된 경우도 여기로 이어짐</t>
   </si>
   <si>
+    <t>"CHUNK_ALL_REJECTED: 모든 청크가 검증 기준에 걸려 제외됐습니다(&lt;파일&gt;, 입력 N건, 사유별 {…})."</t>
+  </si>
+  <si>
+    <t>"CHUNK_VALIDATION_ERROR: 청크 판정 중 오류가 났습니다(&lt;파일&gt; #N): …"</t>
+  </si>
+  <si>
     <t>"Cancelled"</t>
   </si>
   <si>
     <t>• 요청 처리 중 호출한 쪽이 연결을 끊어 처리를 중단
   - 호출 측 대기 시간 만료 또는 요청 취소
   - 서버 오류가 아니므로 호출 측 타임아웃 설정을 확인</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문서의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불량으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판정되어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적재할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: 
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크텍스트가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공백</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄바꿈을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빼면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숫자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기호나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>태그만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한글</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숫자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하나도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">. HTML </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>태그와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구분선은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>세지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: "- - - * * *", "&lt;div&gt;&lt;/div&gt;"
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>③</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깨진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깨진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">(�, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>, GLYPH&lt;…&gt;)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상이면서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공백을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뺀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 30% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>: "��� ����" (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인코딩이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맞지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깨진</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">)
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>④</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내용이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반복되어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대부분을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차지함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반복되고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반복된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부분이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본문의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 50% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: " ... </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문의해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">." </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수십</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>붙음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>⑤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본문이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지나치게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>짧음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판단</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>숫자가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>미만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+       · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본문에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> "1." </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처럼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>글자만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>남은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>섞여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빼고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나머지를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적재</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 
+    → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불량일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오류가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발생</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일부를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빼고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적재한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>경우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정보는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>응답의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> chunk_validation </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>항목으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반환됨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+    · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제외된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(count)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크별</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제외</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사유</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불량</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여부를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판정하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과정에서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오류가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>발생해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문서를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실패로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+  - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판정하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>못한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>청크를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적재하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>않기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전체를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실패로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>처리</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +3336,17 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -255,7 +3361,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -278,26 +3384,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -310,12 +3401,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -619,7 +3704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
@@ -642,7 +3727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="42">
+    <row r="2" spans="1:4" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -656,246 +3741,302 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="42">
+    <row r="3" spans="1:4" ht="42" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="56">
+    <row r="4" spans="1:4" ht="56" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:4" ht="28" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="42">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:4" ht="56" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="42">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:4" ht="42" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="42">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:4" ht="42" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="56">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:4" ht="42" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="42">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:4" ht="56" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="5" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="42" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="11" spans="1:4" ht="42">
-      <c r="A11" s="6" t="s">
+    <row r="12" spans="1:4" ht="42" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="12" spans="1:4" ht="28">
-      <c r="A12" s="6" t="s">
+    <row r="13" spans="1:4" ht="28" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="C13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="13" spans="1:4" ht="42">
-      <c r="A13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="5" t="s">
+    <row r="14" spans="1:4" ht="42" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:4" ht="28">
-      <c r="A14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>35</v>
+    <row r="15" spans="1:4" ht="42" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28">
-      <c r="A15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="5" t="s">
+    <row r="16" spans="1:4" ht="28" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>37</v>
+      <c r="B16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28">
-      <c r="A16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>39</v>
+    <row r="17" spans="1:4" ht="28" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28">
-      <c r="A17" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>41</v>
+    <row r="18" spans="1:4" ht="28" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="42">
-      <c r="A18" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>43</v>
+    <row r="19" spans="1:4" ht="28" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="42">
-      <c r="A19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>45</v>
+    <row r="20" spans="1:4" ht="42" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="320" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="56" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="48" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:D19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:D23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/genon/preprocessor/manual/custom_fields_runtime_exceptions.xlsx
+++ b/genon/preprocessor/manual/custom_fields_runtime_exceptions.xlsx
@@ -1001,8 +1001,8 @@
        · 판단: 글자(한글·영문 등)와 숫자가 하나도 없음. HTML 태그와 표 구분선은 글자로 세지 않음
        · 예: "- - - * * *", "&lt;div&gt;&lt;/div&gt;"
     ③ 깨진 문자가 많음
-       · 판단: 깨진 문자(�, 제어 문자, GLYPH&lt;…&gt;)가 3자 이상이면서 공백을 뺀 전체 글자의 30% 이상
-       · 예: "��� ����" (인코딩이 맞지 않아 깨진 글자)
+       · 판단: 깨진 문자(�, 제어 문자, GLYPH&lt;…&gt;, 잘못된 인코딩으로 바뀐 한글)가 3자 이상이면서 공백을 뺀 전체 글자의 30% 이상
+       · 예: "��� ����", "占쏙옙占쏙옙", "ë³´í—˜ê¸ˆ" (인코딩이 맞지 않아 깨진 글자)
     ④ 같은 내용이 반복되어 본문 대부분을 차지함
        · 판단: 같은 문구/글자가 10번 이상 반복되고, 반복된 부분이 본문의 50% 이상
        · 예: " ... 문의해 주세요." 가 수십 번 이어 붙음
